--- a/jpcore-r4/feature/wg2-pathology/StructureDefinition-jp-diagnosticreport-microbiology.xlsx
+++ b/jpcore-r4/feature/wg2-pathology/StructureDefinition-jp-diagnosticreport-microbiology.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2071" uniqueCount="398">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2070" uniqueCount="396">
   <si>
     <t>Property</t>
   </si>
@@ -585,13 +585,7 @@
     <t>これは、検索、並べ替え、および表示の目的で使用される。</t>
   </si>
   <si>
-    <t>example</t>
-  </si>
-  <si>
-    <t>診断サービスセクションのコード。 / Codes for diagnostic service sections.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/diagnostic-service-sections|4.0.1</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_DiagnosticReportCategory_VS</t>
   </si>
   <si>
     <t xml:space="preserve">pattern:$this}
@@ -819,9 +813,6 @@
   </si>
   <si>
     <t>【JP Core仕様】レポートカテゴリーとして、LoincコードのLP7819-8 (微生物検査/MICRO)を使用する。</t>
-  </si>
-  <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_DiagnosticReportCategory_VS</t>
   </si>
   <si>
     <t>DiagnosticReport.category:first.id</t>
@@ -1238,6 +1229,9 @@
   </si>
   <si>
     <t>すべてのターミノロジの使用がこの一般的なパターンに適合するわけではない。場合によっては、独自の構造を提供する必要がある。</t>
+  </si>
+  <si>
+    <t>example</t>
   </si>
   <si>
     <t>レポートの補助として提供される診断コード。 / Diagnosis codes provided as adjuncts to the report.</t>
@@ -3170,26 +3164,24 @@
         <v>81</v>
       </c>
       <c r="X14" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="Y14" s="2"/>
+      <c r="Z14" t="s" s="2">
         <v>182</v>
       </c>
-      <c r="Y14" t="s" s="2">
+      <c r="AA14" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB14" t="s" s="2">
         <v>183</v>
-      </c>
-      <c r="Z14" t="s" s="2">
-        <v>184</v>
-      </c>
-      <c r="AA14" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB14" t="s" s="2">
-        <v>185</v>
       </c>
       <c r="AC14" s="2"/>
       <c r="AD14" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE14" t="s" s="2">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="AF14" t="s" s="2">
         <v>177</v>
@@ -3210,21 +3202,21 @@
         <v>81</v>
       </c>
       <c r="AL14" t="s" s="2">
+        <v>185</v>
+      </c>
+      <c r="AM14" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="AN14" t="s" s="2">
         <v>187</v>
-      </c>
-      <c r="AM14" t="s" s="2">
-        <v>188</v>
-      </c>
-      <c r="AN14" t="s" s="2">
-        <v>189</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3247,13 +3239,13 @@
         <v>81</v>
       </c>
       <c r="K15" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="L15" t="s" s="2">
+        <v>190</v>
+      </c>
+      <c r="M15" t="s" s="2">
         <v>191</v>
-      </c>
-      <c r="L15" t="s" s="2">
-        <v>192</v>
-      </c>
-      <c r="M15" t="s" s="2">
-        <v>193</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -3304,7 +3296,7 @@
         <v>81</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>79</v>
@@ -3325,7 +3317,7 @@
         <v>81</v>
       </c>
       <c r="AM15" t="s" s="2">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="AN15" t="s" s="2">
         <v>81</v>
@@ -3333,10 +3325,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3365,7 +3357,7 @@
         <v>138</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="N16" t="s" s="2">
         <v>140</v>
@@ -3406,19 +3398,19 @@
         <v>81</v>
       </c>
       <c r="AB16" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="AC16" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="AD16" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE16" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="AF16" t="s" s="2">
         <v>198</v>
-      </c>
-      <c r="AC16" t="s" s="2">
-        <v>199</v>
-      </c>
-      <c r="AD16" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE16" t="s" s="2">
-        <v>186</v>
-      </c>
-      <c r="AF16" t="s" s="2">
-        <v>200</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>79</v>
@@ -3439,7 +3431,7 @@
         <v>81</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="AN16" t="s" s="2">
         <v>81</v>
@@ -3447,10 +3439,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3473,19 +3465,19 @@
         <v>92</v>
       </c>
       <c r="K17" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="L17" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="M17" t="s" s="2">
         <v>202</v>
       </c>
-      <c r="L17" t="s" s="2">
+      <c r="N17" t="s" s="2">
         <v>203</v>
       </c>
-      <c r="M17" t="s" s="2">
+      <c r="O17" t="s" s="2">
         <v>204</v>
-      </c>
-      <c r="N17" t="s" s="2">
-        <v>205</v>
-      </c>
-      <c r="O17" t="s" s="2">
-        <v>206</v>
       </c>
       <c r="P17" t="s" s="2">
         <v>81</v>
@@ -3534,7 +3526,7 @@
         <v>81</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>79</v>
@@ -3552,10 +3544,10 @@
         <v>81</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="AN17" t="s" s="2">
         <v>81</v>
@@ -3563,10 +3555,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3589,13 +3581,13 @@
         <v>81</v>
       </c>
       <c r="K18" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="L18" t="s" s="2">
+        <v>190</v>
+      </c>
+      <c r="M18" t="s" s="2">
         <v>191</v>
-      </c>
-      <c r="L18" t="s" s="2">
-        <v>192</v>
-      </c>
-      <c r="M18" t="s" s="2">
-        <v>193</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -3646,7 +3638,7 @@
         <v>81</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>79</v>
@@ -3667,7 +3659,7 @@
         <v>81</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="AN18" t="s" s="2">
         <v>81</v>
@@ -3675,10 +3667,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3707,7 +3699,7 @@
         <v>138</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="N19" t="s" s="2">
         <v>140</v>
@@ -3748,19 +3740,19 @@
         <v>81</v>
       </c>
       <c r="AB19" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="AC19" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="AD19" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE19" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="AF19" t="s" s="2">
         <v>198</v>
-      </c>
-      <c r="AC19" t="s" s="2">
-        <v>199</v>
-      </c>
-      <c r="AD19" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE19" t="s" s="2">
-        <v>186</v>
-      </c>
-      <c r="AF19" t="s" s="2">
-        <v>200</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>79</v>
@@ -3781,7 +3773,7 @@
         <v>81</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="AN19" t="s" s="2">
         <v>81</v>
@@ -3789,10 +3781,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3818,16 +3810,16 @@
         <v>105</v>
       </c>
       <c r="L20" t="s" s="2">
+        <v>211</v>
+      </c>
+      <c r="M20" t="s" s="2">
+        <v>211</v>
+      </c>
+      <c r="N20" t="s" s="2">
+        <v>212</v>
+      </c>
+      <c r="O20" t="s" s="2">
         <v>213</v>
-      </c>
-      <c r="M20" t="s" s="2">
-        <v>213</v>
-      </c>
-      <c r="N20" t="s" s="2">
-        <v>214</v>
-      </c>
-      <c r="O20" t="s" s="2">
-        <v>215</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>81</v>
@@ -3876,7 +3868,7 @@
         <v>81</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>79</v>
@@ -3894,10 +3886,10 @@
         <v>81</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="AN20" t="s" s="2">
         <v>81</v>
@@ -3905,10 +3897,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3931,16 +3923,16 @@
         <v>92</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="L21" t="s" s="2">
+        <v>218</v>
+      </c>
+      <c r="M21" t="s" s="2">
+        <v>219</v>
+      </c>
+      <c r="N21" t="s" s="2">
         <v>220</v>
-      </c>
-      <c r="M21" t="s" s="2">
-        <v>221</v>
-      </c>
-      <c r="N21" t="s" s="2">
-        <v>222</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -3990,7 +3982,7 @@
         <v>81</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>79</v>
@@ -4008,10 +4000,10 @@
         <v>81</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="AN21" t="s" s="2">
         <v>81</v>
@@ -4019,10 +4011,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4048,14 +4040,14 @@
         <v>111</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" t="s" s="2">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>81</v>
@@ -4104,7 +4096,7 @@
         <v>81</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>79</v>
@@ -4122,10 +4114,10 @@
         <v>81</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="AN22" t="s" s="2">
         <v>81</v>
@@ -4133,10 +4125,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4159,17 +4151,17 @@
         <v>92</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" t="s" s="2">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>81</v>
@@ -4218,7 +4210,7 @@
         <v>81</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>79</v>
@@ -4236,10 +4228,10 @@
         <v>81</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="AN23" t="s" s="2">
         <v>81</v>
@@ -4247,10 +4239,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4273,19 +4265,19 @@
         <v>92</v>
       </c>
       <c r="K24" t="s" s="2">
+        <v>237</v>
+      </c>
+      <c r="L24" t="s" s="2">
+        <v>238</v>
+      </c>
+      <c r="M24" t="s" s="2">
         <v>239</v>
       </c>
-      <c r="L24" t="s" s="2">
+      <c r="N24" t="s" s="2">
         <v>240</v>
       </c>
-      <c r="M24" t="s" s="2">
+      <c r="O24" t="s" s="2">
         <v>241</v>
-      </c>
-      <c r="N24" t="s" s="2">
-        <v>242</v>
-      </c>
-      <c r="O24" t="s" s="2">
-        <v>243</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>81</v>
@@ -4334,7 +4326,7 @@
         <v>81</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>79</v>
@@ -4352,10 +4344,10 @@
         <v>81</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="AN24" t="s" s="2">
         <v>81</v>
@@ -4363,10 +4355,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4389,19 +4381,19 @@
         <v>92</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="L25" t="s" s="2">
+        <v>246</v>
+      </c>
+      <c r="M25" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="N25" t="s" s="2">
         <v>248</v>
       </c>
-      <c r="M25" t="s" s="2">
+      <c r="O25" t="s" s="2">
         <v>249</v>
-      </c>
-      <c r="N25" t="s" s="2">
-        <v>250</v>
-      </c>
-      <c r="O25" t="s" s="2">
-        <v>251</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>81</v>
@@ -4450,7 +4442,7 @@
         <v>81</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>79</v>
@@ -4468,10 +4460,10 @@
         <v>81</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="AN25" t="s" s="2">
         <v>81</v>
@@ -4479,13 +4471,13 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="B26" t="s" s="2">
         <v>177</v>
       </c>
       <c r="C26" t="s" s="2">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="D26" t="s" s="2">
         <v>178</v>
@@ -4510,13 +4502,13 @@
         <v>179</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
@@ -4546,7 +4538,7 @@
       </c>
       <c r="Y26" s="2"/>
       <c r="Z26" t="s" s="2">
-        <v>259</v>
+        <v>182</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>81</v>
@@ -4582,21 +4574,21 @@
         <v>81</v>
       </c>
       <c r="AL26" t="s" s="2">
+        <v>185</v>
+      </c>
+      <c r="AM26" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="AN26" t="s" s="2">
         <v>187</v>
-      </c>
-      <c r="AM26" t="s" s="2">
-        <v>188</v>
-      </c>
-      <c r="AN26" t="s" s="2">
-        <v>189</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4619,13 +4611,13 @@
         <v>81</v>
       </c>
       <c r="K27" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="L27" t="s" s="2">
+        <v>190</v>
+      </c>
+      <c r="M27" t="s" s="2">
         <v>191</v>
-      </c>
-      <c r="L27" t="s" s="2">
-        <v>192</v>
-      </c>
-      <c r="M27" t="s" s="2">
-        <v>193</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -4676,7 +4668,7 @@
         <v>81</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>79</v>
@@ -4697,7 +4689,7 @@
         <v>81</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="AN27" t="s" s="2">
         <v>81</v>
@@ -4705,10 +4697,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4737,7 +4729,7 @@
         <v>138</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="N28" t="s" s="2">
         <v>140</v>
@@ -4778,19 +4770,19 @@
         <v>81</v>
       </c>
       <c r="AB28" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="AC28" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="AD28" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE28" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="AF28" t="s" s="2">
         <v>198</v>
-      </c>
-      <c r="AC28" t="s" s="2">
-        <v>199</v>
-      </c>
-      <c r="AD28" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE28" t="s" s="2">
-        <v>186</v>
-      </c>
-      <c r="AF28" t="s" s="2">
-        <v>200</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>79</v>
@@ -4811,7 +4803,7 @@
         <v>81</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="AN28" t="s" s="2">
         <v>81</v>
@@ -4819,10 +4811,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4845,19 +4837,19 @@
         <v>92</v>
       </c>
       <c r="K29" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="L29" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="M29" t="s" s="2">
         <v>202</v>
       </c>
-      <c r="L29" t="s" s="2">
+      <c r="N29" t="s" s="2">
         <v>203</v>
       </c>
-      <c r="M29" t="s" s="2">
+      <c r="O29" t="s" s="2">
         <v>204</v>
-      </c>
-      <c r="N29" t="s" s="2">
-        <v>205</v>
-      </c>
-      <c r="O29" t="s" s="2">
-        <v>206</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>81</v>
@@ -4906,7 +4898,7 @@
         <v>81</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>79</v>
@@ -4924,10 +4916,10 @@
         <v>81</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="AN29" t="s" s="2">
         <v>81</v>
@@ -4935,10 +4927,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4961,13 +4953,13 @@
         <v>81</v>
       </c>
       <c r="K30" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="L30" t="s" s="2">
+        <v>190</v>
+      </c>
+      <c r="M30" t="s" s="2">
         <v>191</v>
-      </c>
-      <c r="L30" t="s" s="2">
-        <v>192</v>
-      </c>
-      <c r="M30" t="s" s="2">
-        <v>193</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -5018,7 +5010,7 @@
         <v>81</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>79</v>
@@ -5039,7 +5031,7 @@
         <v>81</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="AN30" t="s" s="2">
         <v>81</v>
@@ -5047,10 +5039,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5079,7 +5071,7 @@
         <v>138</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="N31" t="s" s="2">
         <v>140</v>
@@ -5120,19 +5112,19 @@
         <v>81</v>
       </c>
       <c r="AB31" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="AC31" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="AD31" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE31" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="AF31" t="s" s="2">
         <v>198</v>
-      </c>
-      <c r="AC31" t="s" s="2">
-        <v>199</v>
-      </c>
-      <c r="AD31" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE31" t="s" s="2">
-        <v>186</v>
-      </c>
-      <c r="AF31" t="s" s="2">
-        <v>200</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>79</v>
@@ -5153,7 +5145,7 @@
         <v>81</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="AN31" t="s" s="2">
         <v>81</v>
@@ -5161,10 +5153,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5190,16 +5182,16 @@
         <v>105</v>
       </c>
       <c r="L32" t="s" s="2">
+        <v>211</v>
+      </c>
+      <c r="M32" t="s" s="2">
+        <v>211</v>
+      </c>
+      <c r="N32" t="s" s="2">
+        <v>212</v>
+      </c>
+      <c r="O32" t="s" s="2">
         <v>213</v>
-      </c>
-      <c r="M32" t="s" s="2">
-        <v>213</v>
-      </c>
-      <c r="N32" t="s" s="2">
-        <v>214</v>
-      </c>
-      <c r="O32" t="s" s="2">
-        <v>215</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>81</v>
@@ -5248,7 +5240,7 @@
         <v>81</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>79</v>
@@ -5266,10 +5258,10 @@
         <v>81</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="AN32" t="s" s="2">
         <v>81</v>
@@ -5277,10 +5269,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5303,16 +5295,16 @@
         <v>92</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="L33" t="s" s="2">
+        <v>218</v>
+      </c>
+      <c r="M33" t="s" s="2">
+        <v>219</v>
+      </c>
+      <c r="N33" t="s" s="2">
         <v>220</v>
-      </c>
-      <c r="M33" t="s" s="2">
-        <v>221</v>
-      </c>
-      <c r="N33" t="s" s="2">
-        <v>222</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -5362,7 +5354,7 @@
         <v>81</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>79</v>
@@ -5380,10 +5372,10 @@
         <v>81</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="AN33" t="s" s="2">
         <v>81</v>
@@ -5391,10 +5383,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5420,14 +5412,14 @@
         <v>111</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" t="s" s="2">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>81</v>
@@ -5437,7 +5429,7 @@
         <v>81</v>
       </c>
       <c r="S34" t="s" s="2">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="T34" t="s" s="2">
         <v>81</v>
@@ -5476,7 +5468,7 @@
         <v>81</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>79</v>
@@ -5494,10 +5486,10 @@
         <v>81</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="AN34" t="s" s="2">
         <v>81</v>
@@ -5505,10 +5497,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5531,17 +5523,17 @@
         <v>92</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" t="s" s="2">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>81</v>
@@ -5590,7 +5582,7 @@
         <v>81</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>79</v>
@@ -5608,10 +5600,10 @@
         <v>81</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="AN35" t="s" s="2">
         <v>81</v>
@@ -5619,10 +5611,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5645,19 +5637,19 @@
         <v>92</v>
       </c>
       <c r="K36" t="s" s="2">
+        <v>237</v>
+      </c>
+      <c r="L36" t="s" s="2">
+        <v>238</v>
+      </c>
+      <c r="M36" t="s" s="2">
         <v>239</v>
       </c>
-      <c r="L36" t="s" s="2">
+      <c r="N36" t="s" s="2">
         <v>240</v>
       </c>
-      <c r="M36" t="s" s="2">
+      <c r="O36" t="s" s="2">
         <v>241</v>
-      </c>
-      <c r="N36" t="s" s="2">
-        <v>242</v>
-      </c>
-      <c r="O36" t="s" s="2">
-        <v>243</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>81</v>
@@ -5706,7 +5698,7 @@
         <v>81</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>79</v>
@@ -5724,10 +5716,10 @@
         <v>81</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="AN36" t="s" s="2">
         <v>81</v>
@@ -5735,10 +5727,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5761,19 +5753,19 @@
         <v>92</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="L37" t="s" s="2">
+        <v>246</v>
+      </c>
+      <c r="M37" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="N37" t="s" s="2">
         <v>248</v>
       </c>
-      <c r="M37" t="s" s="2">
+      <c r="O37" t="s" s="2">
         <v>249</v>
-      </c>
-      <c r="N37" t="s" s="2">
-        <v>250</v>
-      </c>
-      <c r="O37" t="s" s="2">
-        <v>251</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>81</v>
@@ -5822,7 +5814,7 @@
         <v>81</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>79</v>
@@ -5840,10 +5832,10 @@
         <v>81</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="AN37" t="s" s="2">
         <v>81</v>
@@ -5851,14 +5843,14 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
@@ -5880,10 +5872,10 @@
         <v>179</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -5895,7 +5887,7 @@
         <v>81</v>
       </c>
       <c r="S38" t="s" s="2">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="T38" t="s" s="2">
         <v>81</v>
@@ -5914,7 +5906,7 @@
       </c>
       <c r="Y38" s="2"/>
       <c r="Z38" t="s" s="2">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>81</v>
@@ -5932,7 +5924,7 @@
         <v>81</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>91</v>
@@ -5947,28 +5939,28 @@
         <v>103</v>
       </c>
       <c r="AK38" t="s" s="2">
+        <v>274</v>
+      </c>
+      <c r="AL38" t="s" s="2">
+        <v>275</v>
+      </c>
+      <c r="AM38" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="AN38" t="s" s="2">
         <v>277</v>
-      </c>
-      <c r="AL38" t="s" s="2">
-        <v>278</v>
-      </c>
-      <c r="AM38" t="s" s="2">
-        <v>279</v>
-      </c>
-      <c r="AN38" t="s" s="2">
-        <v>280</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
@@ -5987,19 +5979,19 @@
         <v>92</v>
       </c>
       <c r="K39" t="s" s="2">
+        <v>280</v>
+      </c>
+      <c r="L39" t="s" s="2">
+        <v>281</v>
+      </c>
+      <c r="M39" t="s" s="2">
+        <v>281</v>
+      </c>
+      <c r="N39" t="s" s="2">
+        <v>282</v>
+      </c>
+      <c r="O39" t="s" s="2">
         <v>283</v>
-      </c>
-      <c r="L39" t="s" s="2">
-        <v>284</v>
-      </c>
-      <c r="M39" t="s" s="2">
-        <v>284</v>
-      </c>
-      <c r="N39" t="s" s="2">
-        <v>285</v>
-      </c>
-      <c r="O39" t="s" s="2">
-        <v>286</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>81</v>
@@ -6048,7 +6040,7 @@
         <v>81</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>79</v>
@@ -6063,28 +6055,28 @@
         <v>103</v>
       </c>
       <c r="AK39" t="s" s="2">
+        <v>284</v>
+      </c>
+      <c r="AL39" t="s" s="2">
+        <v>285</v>
+      </c>
+      <c r="AM39" t="s" s="2">
+        <v>286</v>
+      </c>
+      <c r="AN39" t="s" s="2">
         <v>287</v>
-      </c>
-      <c r="AL39" t="s" s="2">
-        <v>288</v>
-      </c>
-      <c r="AM39" t="s" s="2">
-        <v>289</v>
-      </c>
-      <c r="AN39" t="s" s="2">
-        <v>290</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
@@ -6103,19 +6095,19 @@
         <v>92</v>
       </c>
       <c r="K40" t="s" s="2">
+        <v>290</v>
+      </c>
+      <c r="L40" t="s" s="2">
+        <v>291</v>
+      </c>
+      <c r="M40" t="s" s="2">
+        <v>291</v>
+      </c>
+      <c r="N40" t="s" s="2">
+        <v>292</v>
+      </c>
+      <c r="O40" t="s" s="2">
         <v>293</v>
-      </c>
-      <c r="L40" t="s" s="2">
-        <v>294</v>
-      </c>
-      <c r="M40" t="s" s="2">
-        <v>294</v>
-      </c>
-      <c r="N40" t="s" s="2">
-        <v>295</v>
-      </c>
-      <c r="O40" t="s" s="2">
-        <v>296</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>81</v>
@@ -6164,7 +6156,7 @@
         <v>81</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>79</v>
@@ -6179,28 +6171,28 @@
         <v>103</v>
       </c>
       <c r="AK40" t="s" s="2">
+        <v>294</v>
+      </c>
+      <c r="AL40" t="s" s="2">
+        <v>295</v>
+      </c>
+      <c r="AM40" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="AN40" t="s" s="2">
         <v>297</v>
-      </c>
-      <c r="AL40" t="s" s="2">
-        <v>298</v>
-      </c>
-      <c r="AM40" t="s" s="2">
-        <v>299</v>
-      </c>
-      <c r="AN40" t="s" s="2">
-        <v>300</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
@@ -6219,19 +6211,19 @@
         <v>92</v>
       </c>
       <c r="K41" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="L41" t="s" s="2">
+        <v>301</v>
+      </c>
+      <c r="M41" t="s" s="2">
+        <v>301</v>
+      </c>
+      <c r="N41" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="O41" t="s" s="2">
         <v>303</v>
-      </c>
-      <c r="L41" t="s" s="2">
-        <v>304</v>
-      </c>
-      <c r="M41" t="s" s="2">
-        <v>304</v>
-      </c>
-      <c r="N41" t="s" s="2">
-        <v>305</v>
-      </c>
-      <c r="O41" t="s" s="2">
-        <v>306</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>81</v>
@@ -6280,7 +6272,7 @@
         <v>81</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>79</v>
@@ -6295,28 +6287,28 @@
         <v>103</v>
       </c>
       <c r="AK41" t="s" s="2">
+        <v>304</v>
+      </c>
+      <c r="AL41" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="AM41" t="s" s="2">
+        <v>306</v>
+      </c>
+      <c r="AN41" t="s" s="2">
         <v>307</v>
-      </c>
-      <c r="AL41" t="s" s="2">
-        <v>308</v>
-      </c>
-      <c r="AM41" t="s" s="2">
-        <v>309</v>
-      </c>
-      <c r="AN41" t="s" s="2">
-        <v>310</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
@@ -6335,19 +6327,19 @@
         <v>92</v>
       </c>
       <c r="K42" t="s" s="2">
+        <v>310</v>
+      </c>
+      <c r="L42" t="s" s="2">
+        <v>311</v>
+      </c>
+      <c r="M42" t="s" s="2">
+        <v>312</v>
+      </c>
+      <c r="N42" t="s" s="2">
         <v>313</v>
       </c>
-      <c r="L42" t="s" s="2">
+      <c r="O42" t="s" s="2">
         <v>314</v>
-      </c>
-      <c r="M42" t="s" s="2">
-        <v>315</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>316</v>
-      </c>
-      <c r="O42" t="s" s="2">
-        <v>317</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>81</v>
@@ -6396,7 +6388,7 @@
         <v>81</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>79</v>
@@ -6414,25 +6406,25 @@
         <v>81</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>320</v>
+        <v>317</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
@@ -6451,19 +6443,19 @@
         <v>92</v>
       </c>
       <c r="K43" t="s" s="2">
+        <v>320</v>
+      </c>
+      <c r="L43" t="s" s="2">
+        <v>321</v>
+      </c>
+      <c r="M43" t="s" s="2">
+        <v>321</v>
+      </c>
+      <c r="N43" t="s" s="2">
+        <v>322</v>
+      </c>
+      <c r="O43" t="s" s="2">
         <v>323</v>
-      </c>
-      <c r="L43" t="s" s="2">
-        <v>324</v>
-      </c>
-      <c r="M43" t="s" s="2">
-        <v>324</v>
-      </c>
-      <c r="N43" t="s" s="2">
-        <v>325</v>
-      </c>
-      <c r="O43" t="s" s="2">
-        <v>326</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>81</v>
@@ -6512,7 +6504,7 @@
         <v>81</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>79</v>
@@ -6527,28 +6519,28 @@
         <v>103</v>
       </c>
       <c r="AK43" t="s" s="2">
+        <v>324</v>
+      </c>
+      <c r="AL43" t="s" s="2">
+        <v>325</v>
+      </c>
+      <c r="AM43" t="s" s="2">
+        <v>326</v>
+      </c>
+      <c r="AN43" t="s" s="2">
         <v>327</v>
-      </c>
-      <c r="AL43" t="s" s="2">
-        <v>328</v>
-      </c>
-      <c r="AM43" t="s" s="2">
-        <v>329</v>
-      </c>
-      <c r="AN43" t="s" s="2">
-        <v>330</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
@@ -6567,19 +6559,19 @@
         <v>92</v>
       </c>
       <c r="K44" t="s" s="2">
+        <v>320</v>
+      </c>
+      <c r="L44" t="s" s="2">
+        <v>330</v>
+      </c>
+      <c r="M44" t="s" s="2">
+        <v>330</v>
+      </c>
+      <c r="N44" t="s" s="2">
+        <v>331</v>
+      </c>
+      <c r="O44" t="s" s="2">
         <v>323</v>
-      </c>
-      <c r="L44" t="s" s="2">
-        <v>333</v>
-      </c>
-      <c r="M44" t="s" s="2">
-        <v>333</v>
-      </c>
-      <c r="N44" t="s" s="2">
-        <v>334</v>
-      </c>
-      <c r="O44" t="s" s="2">
-        <v>326</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>81</v>
@@ -6628,7 +6620,7 @@
         <v>81</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>79</v>
@@ -6643,24 +6635,24 @@
         <v>103</v>
       </c>
       <c r="AK44" t="s" s="2">
+        <v>324</v>
+      </c>
+      <c r="AL44" t="s" s="2">
+        <v>332</v>
+      </c>
+      <c r="AM44" t="s" s="2">
+        <v>326</v>
+      </c>
+      <c r="AN44" t="s" s="2">
         <v>327</v>
-      </c>
-      <c r="AL44" t="s" s="2">
-        <v>335</v>
-      </c>
-      <c r="AM44" t="s" s="2">
-        <v>329</v>
-      </c>
-      <c r="AN44" t="s" s="2">
-        <v>330</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6683,19 +6675,19 @@
         <v>81</v>
       </c>
       <c r="K45" t="s" s="2">
+        <v>334</v>
+      </c>
+      <c r="L45" t="s" s="2">
+        <v>335</v>
+      </c>
+      <c r="M45" t="s" s="2">
+        <v>335</v>
+      </c>
+      <c r="N45" t="s" s="2">
+        <v>336</v>
+      </c>
+      <c r="O45" t="s" s="2">
         <v>337</v>
-      </c>
-      <c r="L45" t="s" s="2">
-        <v>338</v>
-      </c>
-      <c r="M45" t="s" s="2">
-        <v>338</v>
-      </c>
-      <c r="N45" t="s" s="2">
-        <v>339</v>
-      </c>
-      <c r="O45" t="s" s="2">
-        <v>340</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>81</v>
@@ -6744,7 +6736,7 @@
         <v>81</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>79</v>
@@ -6762,10 +6754,10 @@
         <v>81</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="AN45" t="s" s="2">
         <v>81</v>
@@ -6773,14 +6765,14 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
@@ -6799,19 +6791,19 @@
         <v>81</v>
       </c>
       <c r="K46" t="s" s="2">
+        <v>341</v>
+      </c>
+      <c r="L46" t="s" s="2">
+        <v>342</v>
+      </c>
+      <c r="M46" t="s" s="2">
+        <v>342</v>
+      </c>
+      <c r="N46" t="s" s="2">
+        <v>343</v>
+      </c>
+      <c r="O46" t="s" s="2">
         <v>344</v>
-      </c>
-      <c r="L46" t="s" s="2">
-        <v>345</v>
-      </c>
-      <c r="M46" t="s" s="2">
-        <v>345</v>
-      </c>
-      <c r="N46" t="s" s="2">
-        <v>346</v>
-      </c>
-      <c r="O46" t="s" s="2">
-        <v>347</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>81</v>
@@ -6860,7 +6852,7 @@
         <v>81</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>79</v>
@@ -6878,10 +6870,10 @@
         <v>81</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="AN46" t="s" s="2">
         <v>81</v>
@@ -6889,10 +6881,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -6915,16 +6907,16 @@
         <v>81</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -6974,7 +6966,7 @@
         <v>81</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>79</v>
@@ -6995,7 +6987,7 @@
         <v>81</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="AN47" t="s" s="2">
         <v>81</v>
@@ -7003,14 +6995,14 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
@@ -7029,19 +7021,19 @@
         <v>92</v>
       </c>
       <c r="K48" t="s" s="2">
+        <v>354</v>
+      </c>
+      <c r="L48" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="M48" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="N48" t="s" s="2">
+        <v>356</v>
+      </c>
+      <c r="O48" t="s" s="2">
         <v>357</v>
-      </c>
-      <c r="L48" t="s" s="2">
-        <v>358</v>
-      </c>
-      <c r="M48" t="s" s="2">
-        <v>358</v>
-      </c>
-      <c r="N48" t="s" s="2">
-        <v>359</v>
-      </c>
-      <c r="O48" t="s" s="2">
-        <v>360</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>81</v>
@@ -7090,7 +7082,7 @@
         <v>81</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>79</v>
@@ -7108,10 +7100,10 @@
         <v>81</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="AN48" t="s" s="2">
         <v>81</v>
@@ -7119,10 +7111,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7145,13 +7137,13 @@
         <v>81</v>
       </c>
       <c r="K49" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="L49" t="s" s="2">
+        <v>190</v>
+      </c>
+      <c r="M49" t="s" s="2">
         <v>191</v>
-      </c>
-      <c r="L49" t="s" s="2">
-        <v>192</v>
-      </c>
-      <c r="M49" t="s" s="2">
-        <v>193</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -7202,7 +7194,7 @@
         <v>81</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>79</v>
@@ -7223,7 +7215,7 @@
         <v>81</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="AN49" t="s" s="2">
         <v>81</v>
@@ -7231,10 +7223,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7263,7 +7255,7 @@
         <v>138</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="N50" t="s" s="2">
         <v>140</v>
@@ -7316,7 +7308,7 @@
         <v>81</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>79</v>
@@ -7337,7 +7329,7 @@
         <v>81</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="AN50" t="s" s="2">
         <v>81</v>
@@ -7345,14 +7337,14 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
@@ -7374,10 +7366,10 @@
         <v>137</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="N51" t="s" s="2">
         <v>140</v>
@@ -7432,7 +7424,7 @@
         <v>81</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>79</v>
@@ -7461,10 +7453,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7487,19 +7479,19 @@
         <v>81</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="L52" t="s" s="2">
+        <v>367</v>
+      </c>
+      <c r="M52" t="s" s="2">
+        <v>368</v>
+      </c>
+      <c r="N52" t="s" s="2">
+        <v>369</v>
+      </c>
+      <c r="O52" t="s" s="2">
         <v>370</v>
-      </c>
-      <c r="M52" t="s" s="2">
-        <v>371</v>
-      </c>
-      <c r="N52" t="s" s="2">
-        <v>372</v>
-      </c>
-      <c r="O52" t="s" s="2">
-        <v>373</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>81</v>
@@ -7548,7 +7540,7 @@
         <v>81</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>79</v>
@@ -7569,7 +7561,7 @@
         <v>81</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="AN52" t="s" s="2">
         <v>81</v>
@@ -7577,10 +7569,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7603,13 +7595,13 @@
         <v>92</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -7660,7 +7652,7 @@
         <v>81</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>91</v>
@@ -7681,7 +7673,7 @@
         <v>81</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="AN53" t="s" s="2">
         <v>81</v>
@@ -7689,14 +7681,14 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
@@ -7715,17 +7707,17 @@
         <v>81</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" t="s" s="2">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>81</v>
@@ -7774,7 +7766,7 @@
         <v>81</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>79</v>
@@ -7792,10 +7784,10 @@
         <v>81</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="AN54" t="s" s="2">
         <v>81</v>
@@ -7803,10 +7795,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -7832,13 +7824,13 @@
         <v>179</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -7864,13 +7856,13 @@
         <v>81</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>182</v>
+        <v>386</v>
       </c>
       <c r="Y55" t="s" s="2">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="Z55" t="s" s="2">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>81</v>
@@ -7888,7 +7880,7 @@
         <v>81</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>79</v>
@@ -7906,10 +7898,10 @@
         <v>81</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="AN55" t="s" s="2">
         <v>81</v>
@@ -7917,10 +7909,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -7943,19 +7935,19 @@
         <v>81</v>
       </c>
       <c r="K56" t="s" s="2">
+        <v>391</v>
+      </c>
+      <c r="L56" t="s" s="2">
+        <v>392</v>
+      </c>
+      <c r="M56" t="s" s="2">
+        <v>392</v>
+      </c>
+      <c r="N56" t="s" s="2">
         <v>393</v>
       </c>
-      <c r="L56" t="s" s="2">
+      <c r="O56" t="s" s="2">
         <v>394</v>
-      </c>
-      <c r="M56" t="s" s="2">
-        <v>394</v>
-      </c>
-      <c r="N56" t="s" s="2">
-        <v>395</v>
-      </c>
-      <c r="O56" t="s" s="2">
-        <v>396</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>81</v>
@@ -8004,7 +7996,7 @@
         <v>81</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>79</v>
@@ -8022,10 +8014,10 @@
         <v>81</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="AN56" t="s" s="2">
         <v>81</v>
